--- a/assets/constructions/examples/ctd_dsp.xlsx
+++ b/assets/constructions/examples/ctd_dsp.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,48 +539,65 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MDP 3510</t>
+          <t>118450 8X69</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PALBIT</t>
+          <t>GARANT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MDP</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>PMKNS</t>
-        </is>
-      </c>
+          <t>118450</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>35</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>PALB_Pilot_B:10</t>
+          <t>HB-8</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -590,12 +607,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PALB_Pilot_B</t>
+          <t>HOFF_Pilot_HB08</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Palbit</t>
+          <t>Hoffmann</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -604,11 +621,11 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -619,19 +636,26 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
-          <t>VHM</t>
+          <t>HSS</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2020 / Palbit General Catalogue EN</t>
-        </is>
-      </c>
+          <t>2020 / hoffmann-group.ru</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MDP 4516</t>
+          <t>MDP 3812</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,24 +675,24 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PALB_Pilot_B:16</t>
+          <t>PALB_Pilot_B:12</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -713,42 +737,61 @@
       <c r="V3" t="inlineStr">
         <is>
           <t>2020 / Palbit General Catalogue EN</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>98.94</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>9095.92</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>118555 6X48</t>
+          <t>118450 8X94</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOLEX</t>
+          <t>GARANT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118555</t>
+          <t>118450</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>HB-6</t>
+          <t>HB-8</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -758,7 +801,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>HOFF_Pilot_HB06</t>
+          <t>HOFF_Pilot_HB08</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -795,11 +838,18 @@
           <t>2020 / hoffmann-group.ru</t>
         </is>
       </c>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDP 3812</t>
+          <t>MDP 2508</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -819,24 +869,24 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>PALB_Pilot_B:12</t>
+          <t>PALB_Pilot_A:8</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -846,7 +896,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>PALB_Pilot_B</t>
+          <t>PALB_Pilot_A</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -856,7 +906,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -881,42 +931,69 @@
       <c r="V5" t="inlineStr">
         <is>
           <t>2020 / Palbit General Catalogue EN</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>53.93</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>4957.98</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>118550 8X48</t>
+          <t>MDP 3510</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GARANT</t>
+          <t>PALBIT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>118550</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>MDP</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>48</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>HB-8</t>
+          <t>PALB_Pilot_B:10</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -926,12 +1003,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>HOFF_Pilot_HB08</t>
+          <t>PALB_Pilot_B</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Hoffmann</t>
+          <t>Palbit</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -940,11 +1017,11 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>X</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -955,12 +1032,31 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2020 / hoffmann-group.ru</t>
+          <t>2020 / Palbit General Catalogue EN</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>77.81</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>7153.36</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
         </is>
       </c>
     </row>
